--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T16:19:33+00:00</t>
+    <t>2026-06-15T16:22:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T16:22:03+00:00</t>
+    <t>2026-06-22T07:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="480">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T07:18:24+00:00</t>
+    <t>2026-07-23T09:21:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -459,40 +459,24 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>ServiceRequest.extension:interpretation</t>
-  </si>
-  <si>
-    <t>interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-interpretation-extension|2.2.0}
+    <t>ServiceRequest.extension:method</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-method-extension|2.2.0}
 </t>
   </si>
   <si>
-    <t>Interprétation</t>
-  </si>
-  <si>
-    <t>Extension permettant de spécifier une interprétation.</t>
+    <t>Méthode</t>
+  </si>
+  <si>
+    <t>Extension permettant d'indiquer la méthode utilisée : techniques biologiques (ex. : titration, agglutination…), techniques d'imagerie dans les demandes d'examen (ultrasound, tomographie, IRM…), des méthodes de mesure spécifiques, etc.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>ServiceRequest.extension:method</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-method-extension|2.2.0}
-</t>
-  </si>
-  <si>
-    <t>Méthode</t>
-  </si>
-  <si>
-    <t>Extension permettant d'indiquer la méthode utilisée : techniques biologiques (ex. : titration, agglutination…), techniques d'imagerie dans les demandes d'examen (ultrasound, tomographie, IRM…), des méthodes de mesure spécifiques, etc.</t>
   </si>
   <si>
     <t>ServiceRequest.modifierExtension</t>
@@ -1839,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO52"/>
+  <dimension ref="A1:AO51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.24609375" customWidth="true" bestFit="true"/>
@@ -3059,41 +3043,43 @@
         <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="O11" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3141,7 +3127,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3150,7 +3136,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>142</v>
@@ -3162,7 +3148,7 @@
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>82</v>
@@ -3173,14 +3159,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3193,26 +3179,24 @@
         <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="J12" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3248,19 +3232,17 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3272,32 +3254,34 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3306,7 +3290,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3318,16 +3302,16 @@
         <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3365,17 +3349,19 @@
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AC13" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3390,31 +3376,29 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3423,7 +3407,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -3435,16 +3419,16 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3494,7 +3478,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3509,27 +3493,27 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>171</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3552,16 +3536,16 @@
         <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3611,7 +3595,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3626,13 +3610,13 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -3650,7 +3634,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3669,17 +3653,15 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3743,13 +3725,13 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
@@ -3760,14 +3742,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3786,13 +3768,13 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3843,7 +3825,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3858,13 +3840,13 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
@@ -3875,21 +3857,21 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -3901,16 +3883,20 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -3958,13 +3944,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -3973,13 +3959,13 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
@@ -3990,18 +3976,18 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -4010,26 +3996,24 @@
         <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4053,13 +4037,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4077,10 +4061,10 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>91</v>
@@ -4092,27 +4076,27 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>82</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4138,13 +4122,13 @@
         <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4170,13 +4154,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4194,7 +4178,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>91</v>
@@ -4209,27 +4193,27 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>222</v>
+        <v>134</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4240,30 +4224,32 @@
         <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4287,37 +4273,37 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="Y21" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AG21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4326,16 +4312,16 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>134</v>
+        <v>239</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4343,10 +4329,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4354,10 +4340,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4369,24 +4355,22 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>236</v>
+        <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q22" s="2"/>
+      <c r="Q22" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="R22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4406,37 +4390,37 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="Y22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4445,16 +4429,16 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4462,10 +4446,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4482,27 +4466,31 @@
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q23" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="R23" t="s" s="2">
         <v>82</v>
@@ -4523,31 +4511,31 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="Z23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4562,16 +4550,16 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4579,18 +4567,18 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
@@ -4599,76 +4587,72 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="P24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q24" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="R24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4683,35 +4667,35 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>91</v>
@@ -4726,16 +4710,16 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4761,13 +4745,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4785,46 +4769,46 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4840,20 +4824,18 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4878,13 +4860,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4902,53 +4884,53 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -4960,7 +4942,7 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>287</v>
+        <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>288</v>
@@ -4968,7 +4950,9 @@
       <c r="M27" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N27" s="2"/>
+      <c r="N27" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5005,31 +4989,31 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5038,7 +5022,7 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
@@ -5056,7 +5040,7 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5072,21 +5056,23 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>136</v>
+        <v>293</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5122,19 +5108,19 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5146,16 +5132,16 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
@@ -5166,10 +5152,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5180,7 +5166,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5192,19 +5178,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5253,13 +5239,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5271,10 +5257,10 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
@@ -5285,10 +5271,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5311,19 +5297,17 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5372,7 +5356,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5390,10 +5374,10 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>82</v>
@@ -5404,10 +5388,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5415,7 +5399,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>91</v>
@@ -5430,18 +5414,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>318</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5489,10 +5471,10 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>91</v>
@@ -5504,35 +5486,35 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>91</v>
@@ -5547,13 +5529,13 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5604,10 +5586,10 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>91</v>
@@ -5619,35 +5601,35 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>91</v>
@@ -5662,13 +5644,13 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5719,7 +5701,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5734,35 +5716,35 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
@@ -5777,13 +5759,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5810,13 +5792,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -5834,7 +5816,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5849,31 +5831,31 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5892,13 +5874,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5925,13 +5907,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -5949,7 +5931,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5964,31 +5946,31 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6007,15 +5989,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6064,7 +6048,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6079,31 +6063,31 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6122,16 +6106,16 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>369</v>
+        <v>231</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6157,13 +6141,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6181,7 +6165,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6196,38 +6180,38 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6239,16 +6223,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>236</v>
+        <v>386</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6274,37 +6258,37 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AA38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6313,16 +6297,16 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6330,14 +6314,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6356,17 +6340,15 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>391</v>
+        <v>231</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6391,13 +6373,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6415,7 +6397,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6430,16 +6412,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6447,10 +6429,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6473,13 +6455,13 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>236</v>
+        <v>400</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6506,13 +6488,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6530,7 +6512,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6551,10 +6533,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6562,10 +6544,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6588,15 +6570,17 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6621,13 +6605,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6645,7 +6629,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6660,16 +6644,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6677,10 +6661,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6703,16 +6687,16 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>236</v>
+        <v>414</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6738,31 +6722,31 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="Z42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6777,16 +6761,16 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6794,10 +6778,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6817,20 +6801,18 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6879,7 +6861,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6894,16 +6876,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6911,14 +6893,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6937,15 +6919,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -6994,7 +6978,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7009,13 +6993,13 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7026,14 +7010,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7049,19 +7033,19 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7111,7 +7095,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7126,13 +7110,13 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7143,14 +7127,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7169,18 +7153,20 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>443</v>
+        <v>231</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7204,13 +7190,11 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7228,7 +7212,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7246,32 +7230,32 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>81</v>
@@ -7283,23 +7267,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>236</v>
+        <v>456</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7323,29 +7303,29 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7360,38 +7340,40 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>447</v>
+        <v>280</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>460</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7403,13 +7385,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7448,17 +7430,19 @@
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7473,30 +7457,30 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>82</v>
@@ -7518,13 +7502,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7575,7 +7559,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7590,37 +7574,35 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>91</v>
@@ -7632,16 +7614,16 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>461</v>
+        <v>282</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7692,13 +7674,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -7707,27 +7689,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7738,7 +7720,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -7747,10 +7729,10 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>287</v>
+        <v>474</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>475</v>
@@ -7758,7 +7740,9 @@
       <c r="M51" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="N51" s="2"/>
+      <c r="N51" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7807,13 +7791,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -7822,135 +7806,18 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>285</v>
+        <v>134</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:21:02+00:00</t>
+    <t>2026-07-23T09:32:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>81</v>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:32:23+00:00</t>
+    <t>2026-07-23T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="453">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:36:51+00:00</t>
+    <t>2026-07-23T09:46:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -869,7 +869,7 @@
 </t>
   </si>
   <si>
-    <t>Additional order information</t>
+    <t>Résultat de la demande</t>
   </si>
   <si>
     <t>Additional details and instructions about the how the services are to be delivered.   For example, and order for a urinary catheter may have an order detail for an external or indwelling catheter, or an order for a bandage may require additional instructions specifying how the bandage should be applied.</t>
@@ -891,596 +891,514 @@
     <t>NTE</t>
   </si>
   <si>
-    <t>ServiceRequest.orderDetail.id</t>
+    <t>ServiceRequest.quantity[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+RatioRange</t>
+  </si>
+  <si>
+    <t>Service amount</t>
+  </si>
+  <si>
+    <t>An amount of service being requested which can be a quantity ( for example $1,500 home modification), a ratio ( for example, 20 half day visits per month), or a range (2.0 to 1.8 Gy per fraction).</t>
+  </si>
+  <si>
+    <t>When ordering a service the number of service items may need to be specified separately from the the service item.</t>
+  </si>
+  <si>
+    <t>.quantity</t>
+  </si>
+  <si>
+    <t>ServiceRequest.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Location|4.0.1|Device|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Individual or Entity the service is ordered for</t>
+  </si>
+  <si>
+    <t>On whom or what the service is to be performed. This is usually a human patient, but can also be requested on animals, groups of humans or animals, devices such as dialysis machines, or even locations (typically for environmental scans).</t>
+  </si>
+  <si>
+    <t>Request.subject</t>
+  </si>
+  <si>
+    <t>PID</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].role</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>ClinicalStatement.subject</t>
+  </si>
+  <si>
+    <t>ServiceRequest.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">context
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Encounter in which the request was created</t>
+  </si>
+  <si>
+    <t>An encounter that provides additional information about the healthcare context in which this request is made.</t>
+  </si>
+  <si>
+    <t>Request.encounter</t>
+  </si>
+  <si>
+    <t>PV1</t>
+  </si>
+  <si>
+    <t>.inboundRelationship(typeCode=COMP].source[classCode&lt;=PCPR, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>ClinicalStatement.encounter</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">schedule
+</t>
+  </si>
+  <si>
+    <t>dateTime
+PeriodTiming</t>
+  </si>
+  <si>
+    <t>Date prévisionnelle de l'examen, du suivi, de l'objectif</t>
+  </si>
+  <si>
+    <t>The date/time at which the requested service should occur.</t>
+  </si>
+  <si>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>TQ1/TQ2, OBR-7/OBR-8</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.planned</t>
+  </si>
+  <si>
+    <t>Procedure.procedureSchedule</t>
+  </si>
+  <si>
+    <t>ServiceRequest.asNeeded[x]</t>
+  </si>
+  <si>
+    <t>boolean
+CodeableConcept</t>
+  </si>
+  <si>
+    <t>Preconditions for service</t>
+  </si>
+  <si>
+    <t>If a CodeableConcept is present, it indicates the pre-condition for performing the service.  For example "pain", "on flare-up", etc.</t>
+  </si>
+  <si>
+    <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
+  </si>
+  <si>
+    <t>Proposal.prnReason.reason</t>
+  </si>
+  <si>
+    <t>ServiceRequest.authoredOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orderedOn
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date request signed</t>
+  </si>
+  <si>
+    <t>When the request transitioned to being actionable.</t>
+  </si>
+  <si>
+    <t>Request.authoredOn</t>
+  </si>
+  <si>
+    <t>ORC.9,  RF1-7 / RF1-9</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Proposal.proposedAtTime</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester</t>
+  </si>
+  <si>
+    <t>author
+orderer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who/what is requesting service</t>
+  </si>
+  <si>
+    <t>The individual who initiated the request and has responsibility for its activation.</t>
+  </si>
+  <si>
+    <t>This not the dispatcher, but rather who is the authorizer.  This element is not intended to handle delegation which would generally be managed through the Provenance resource.</t>
+  </si>
+  <si>
+    <t>Request.requester</t>
+  </si>
+  <si>
+    <t>ORC.12, PRT</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>ClinicalStatement.statementAuthor</t>
+  </si>
+  <si>
+    <t>ServiceRequest.performerType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">specialty
+</t>
+  </si>
+  <si>
+    <t>Performer role</t>
+  </si>
+  <si>
+    <t>Desired type of performer for doing the requested service.</t>
+  </si>
+  <si>
+    <t>This is a  role, not  a participation type.  In other words, does not describe the task but describes the capacity.  For example, “compounding pharmacy”, “psychiatrist” or “internal referral”.</t>
+  </si>
+  <si>
+    <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/participant-role|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.performerType</t>
+  </si>
+  <si>
+    <t>PRT, RF!-3</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF].role[scoper.determinerCode=KIND].code</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>ServiceRequest.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">request recipient
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Requested performer</t>
+  </si>
+  <si>
+    <t>The desired performer for doing the requested service.  For example, the surgeon, dermatopathologist, endoscopist, etc.</t>
+  </si>
+  <si>
+    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
+  </si>
+  <si>
+    <t>Request.performer</t>
+  </si>
+  <si>
+    <t>PRT, Practitioner: PRD-2/PRD-7 where PRD-3 = RT; Organization: PRD-10 where PRD-3 = RT</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF].role[scoper.determinerCode=INSTANCE]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.locationCode</t>
+  </si>
+  <si>
+    <t>Requested location</t>
+  </si>
+  <si>
+    <t>The preferred location(s) where the procedure should actually happen in coded or free text form. E.g. at home or nursing day care center.</t>
+  </si>
+  <si>
+    <t>A location type where services are delivered.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType|3.0.0</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=LOC].role[scoper.determinerCode=KIND].code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.locationReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>A reference to the the preferred location(s) where the procedure should actually happen. E.g. at home or nursing day care center.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=LOC].role[scoper.determinerCode=INSTANCE]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.reasonCode</t>
+  </si>
+  <si>
+    <t>Explanation/Justification for procedure or service</t>
+  </si>
+  <si>
+    <t>An explanation or justification for why this service is being requested in coded or textual form.   This is often for billing purposes.  May relate to the resources referred to in `supportingInfo`.</t>
+  </si>
+  <si>
+    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4/servicerequest-example-di.html).</t>
+  </si>
+  <si>
+    <t>Diagnosis or problem codes justifying the reason for requesting the service investigation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.reasonCode</t>
+  </si>
+  <si>
+    <t>ORC.16, RF1-10</t>
+  </si>
+  <si>
+    <t>.reasonCode</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.reasonReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Explanation/Justification for service or service</t>
+  </si>
+  <si>
+    <t>Indicates another resource that provides a justification for why this service is being requested.   May relate to the resources referred to in `supportingInfo`.</t>
+  </si>
+  <si>
+    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.    To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise when referencing  *DiagnosticReport*  it should contain a finding  in `DiagnosticReport.conclusion` and/or `DiagnosticReport.conclusionCode`.   When using a reference to *DocumentReference*, the target document should contain clear findings language providing the relevant reason for this service request.  Use  the CodeableConcept text element in `ServiceRequest.reasonCode` if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4/servicerequest-example-di.html).</t>
+  </si>
+  <si>
+    <t>Request.reasonReference</t>
+  </si>
+  <si>
+    <t>ORC.16</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RSON].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Associated insurance coverage</t>
+  </si>
+  <si>
+    <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be needed for delivering the requested service.</t>
+  </si>
+  <si>
+    <t>Request.insurance</t>
+  </si>
+  <si>
+    <t>IN1/IN2</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COVBY].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.supportingInfo</t>
+  </si>
+  <si>
+    <t>Ask at order entry question
+AOE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Additional clinical information</t>
+  </si>
+  <si>
+    <t>Additional clinical information about the patient or specimen that may influence the services or their interpretations.     This information includes diagnosis, clinical findings and other observations.  In laboratory ordering these are typically referred to as "ask at order entry questions (AOEs)".  This includes observations explicitly requested by the producer (filler) to provide context or supporting information needed to complete the order. For example,  reporting the amount of inspired oxygen for blood gas measurements.</t>
+  </si>
+  <si>
+    <t>To represent information about how the services are to be delivered use the `instructions` element.</t>
+  </si>
+  <si>
+    <t>Request.supportingInfo</t>
+  </si>
+  <si>
+    <t>Accompanying segments</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=PERT].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.specimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Procedure Samples</t>
+  </si>
+  <si>
+    <t>One or more specimens that the laboratory procedure will use.</t>
+  </si>
+  <si>
+    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4/specimen.html) resource points to the ServiceRequest.</t>
+  </si>
+  <si>
+    <t>SPM</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SPC].role</t>
+  </si>
+  <si>
+    <t>ServiceRequest.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">location
+</t>
+  </si>
+  <si>
+    <t>Cible</t>
+  </si>
+  <si>
+    <t>Anatomic location where the procedure should be performed. This is the target site.</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
+  </si>
+  <si>
+    <t>Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+  </si>
+  <si>
+    <t>targetSiteCode</t>
+  </si>
+  <si>
+    <t>Procedure.targetBodySite</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Justification de la demande d'examen / Finalité de l'examen</t>
+  </si>
+  <si>
+    <t>Any other notes and comments made about the service request. For example, internal billing notes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:text}
+</t>
+  </si>
+  <si>
+    <t>Request.note</t>
+  </si>
+  <si>
+    <t>.inboundRelationship(typeCode=SUBJ].source[classCode=ANNGEN, moodCode=EVN].value[xsi:type=ST]</t>
+  </si>
+  <si>
+    <t>ClinicalStatement.additionalText</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:finaliteExamen</t>
+  </si>
+  <si>
+    <t>finaliteExamen</t>
+  </si>
+  <si>
+    <t>Finalité de l'examen demandé</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande</t>
+  </si>
+  <si>
+    <t>justificationDemande</t>
+  </si>
+  <si>
+    <t>Justification de la demande d'examen</t>
+  </si>
+  <si>
+    <t>ServiceRequest.patientInstruction</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Résultat de la demande</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>ServiceRequest.quantity[x]</t>
-  </si>
-  <si>
-    <t>Quantity
-RatioRange</t>
-  </si>
-  <si>
-    <t>Service amount</t>
-  </si>
-  <si>
-    <t>An amount of service being requested which can be a quantity ( for example $1,500 home modification), a ratio ( for example, 20 half day visits per month), or a range (2.0 to 1.8 Gy per fraction).</t>
-  </si>
-  <si>
-    <t>When ordering a service the number of service items may need to be specified separately from the the service item.</t>
-  </si>
-  <si>
-    <t>.quantity</t>
-  </si>
-  <si>
-    <t>ServiceRequest.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Location|4.0.1|Device|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Individual or Entity the service is ordered for</t>
-  </si>
-  <si>
-    <t>On whom or what the service is to be performed. This is usually a human patient, but can also be requested on animals, groups of humans or animals, devices such as dialysis machines, or even locations (typically for environmental scans).</t>
-  </si>
-  <si>
-    <t>Request.subject</t>
-  </si>
-  <si>
-    <t>PID</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].role</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>ClinicalStatement.subject</t>
-  </si>
-  <si>
-    <t>ServiceRequest.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">context
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Encounter in which the request was created</t>
-  </si>
-  <si>
-    <t>An encounter that provides additional information about the healthcare context in which this request is made.</t>
-  </si>
-  <si>
-    <t>Request.encounter</t>
-  </si>
-  <si>
-    <t>PV1</t>
-  </si>
-  <si>
-    <t>.inboundRelationship(typeCode=COMP].source[classCode&lt;=PCPR, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>ClinicalStatement.encounter</t>
-  </si>
-  <si>
-    <t>ServiceRequest.occurrence[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">schedule
-</t>
-  </si>
-  <si>
-    <t>dateTime
-PeriodTiming</t>
-  </si>
-  <si>
-    <t>Date prévisionnelle de l'examen, du suivi, de l'objectif</t>
-  </si>
-  <si>
-    <t>The date/time at which the requested service should occur.</t>
-  </si>
-  <si>
-    <t>Request.occurrence[x]</t>
-  </si>
-  <si>
-    <t>TQ1/TQ2, OBR-7/OBR-8</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.planned</t>
-  </si>
-  <si>
-    <t>Procedure.procedureSchedule</t>
-  </si>
-  <si>
-    <t>ServiceRequest.asNeeded[x]</t>
-  </si>
-  <si>
-    <t>boolean
-CodeableConcept</t>
-  </si>
-  <si>
-    <t>Preconditions for service</t>
-  </si>
-  <si>
-    <t>If a CodeableConcept is present, it indicates the pre-condition for performing the service.  For example "pain", "on flare-up", etc.</t>
-  </si>
-  <si>
-    <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
-  </si>
-  <si>
-    <t>Proposal.prnReason.reason</t>
-  </si>
-  <si>
-    <t>ServiceRequest.authoredOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderedOn
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date request signed</t>
-  </si>
-  <si>
-    <t>When the request transitioned to being actionable.</t>
-  </si>
-  <si>
-    <t>Request.authoredOn</t>
-  </si>
-  <si>
-    <t>ORC.9,  RF1-7 / RF1-9</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Proposal.proposedAtTime</t>
-  </si>
-  <si>
-    <t>ServiceRequest.requester</t>
-  </si>
-  <si>
-    <t>author
-orderer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who/what is requesting service</t>
-  </si>
-  <si>
-    <t>The individual who initiated the request and has responsibility for its activation.</t>
-  </si>
-  <si>
-    <t>This not the dispatcher, but rather who is the authorizer.  This element is not intended to handle delegation which would generally be managed through the Provenance resource.</t>
-  </si>
-  <si>
-    <t>Request.requester</t>
-  </si>
-  <si>
-    <t>ORC.12, PRT</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>ClinicalStatement.statementAuthor</t>
-  </si>
-  <si>
-    <t>ServiceRequest.performerType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">specialty
-</t>
-  </si>
-  <si>
-    <t>Performer role</t>
-  </si>
-  <si>
-    <t>Desired type of performer for doing the requested service.</t>
-  </si>
-  <si>
-    <t>This is a  role, not  a participation type.  In other words, does not describe the task but describes the capacity.  For example, “compounding pharmacy”, “psychiatrist” or “internal referral”.</t>
-  </si>
-  <si>
-    <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/participant-role|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.performerType</t>
-  </si>
-  <si>
-    <t>PRT, RF!-3</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF].role[scoper.determinerCode=KIND].code</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>ServiceRequest.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">request recipient
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Requested performer</t>
-  </si>
-  <si>
-    <t>The desired performer for doing the requested service.  For example, the surgeon, dermatopathologist, endoscopist, etc.</t>
-  </si>
-  <si>
-    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
-  </si>
-  <si>
-    <t>Request.performer</t>
-  </si>
-  <si>
-    <t>PRT, Practitioner: PRD-2/PRD-7 where PRD-3 = RT; Organization: PRD-10 where PRD-3 = RT</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF].role[scoper.determinerCode=INSTANCE]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationCode</t>
-  </si>
-  <si>
-    <t>Requested location</t>
-  </si>
-  <si>
-    <t>The preferred location(s) where the procedure should actually happen in coded or free text form. E.g. at home or nursing day care center.</t>
-  </si>
-  <si>
-    <t>A location type where services are delivered.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType|3.0.0</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=LOC].role[scoper.determinerCode=KIND].code</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>A reference to the the preferred location(s) where the procedure should actually happen. E.g. at home or nursing day care center.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=LOC].role[scoper.determinerCode=INSTANCE]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode</t>
-  </si>
-  <si>
-    <t>Explanation/Justification for procedure or service</t>
-  </si>
-  <si>
-    <t>An explanation or justification for why this service is being requested in coded or textual form.   This is often for billing purposes.  May relate to the resources referred to in `supportingInfo`.</t>
-  </si>
-  <si>
-    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4/servicerequest-example-di.html).</t>
-  </si>
-  <si>
-    <t>Diagnosis or problem codes justifying the reason for requesting the service investigation.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.reasonCode</t>
-  </si>
-  <si>
-    <t>ORC.16, RF1-10</t>
-  </si>
-  <si>
-    <t>.reasonCode</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Explanation/Justification for service or service</t>
-  </si>
-  <si>
-    <t>Indicates another resource that provides a justification for why this service is being requested.   May relate to the resources referred to in `supportingInfo`.</t>
-  </si>
-  <si>
-    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.    To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise when referencing  *DiagnosticReport*  it should contain a finding  in `DiagnosticReport.conclusion` and/or `DiagnosticReport.conclusionCode`.   When using a reference to *DocumentReference*, the target document should contain clear findings language providing the relevant reason for this service request.  Use  the CodeableConcept text element in `ServiceRequest.reasonCode` if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4/servicerequest-example-di.html).</t>
-  </si>
-  <si>
-    <t>Request.reasonReference</t>
-  </si>
-  <si>
-    <t>ORC.16</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RSON].target</t>
-  </si>
-  <si>
-    <t>ServiceRequest.insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Associated insurance coverage</t>
-  </si>
-  <si>
-    <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be needed for delivering the requested service.</t>
-  </si>
-  <si>
-    <t>Request.insurance</t>
-  </si>
-  <si>
-    <t>IN1/IN2</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COVBY].target</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo</t>
-  </si>
-  <si>
-    <t>Ask at order entry question
-AOE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Additional clinical information</t>
-  </si>
-  <si>
-    <t>Additional clinical information about the patient or specimen that may influence the services or their interpretations.     This information includes diagnosis, clinical findings and other observations.  In laboratory ordering these are typically referred to as "ask at order entry questions (AOEs)".  This includes observations explicitly requested by the producer (filler) to provide context or supporting information needed to complete the order. For example,  reporting the amount of inspired oxygen for blood gas measurements.</t>
-  </si>
-  <si>
-    <t>To represent information about how the services are to be delivered use the `instructions` element.</t>
-  </si>
-  <si>
-    <t>Request.supportingInfo</t>
-  </si>
-  <si>
-    <t>Accompanying segments</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=PERT].target</t>
-  </si>
-  <si>
-    <t>ServiceRequest.specimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Procedure Samples</t>
-  </si>
-  <si>
-    <t>One or more specimens that the laboratory procedure will use.</t>
-  </si>
-  <si>
-    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4/specimen.html) resource points to the ServiceRequest.</t>
-  </si>
-  <si>
-    <t>SPM</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SPC].role</t>
-  </si>
-  <si>
-    <t>ServiceRequest.bodySite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">location
-</t>
-  </si>
-  <si>
-    <t>Cible</t>
-  </si>
-  <si>
-    <t>Anatomic location where the procedure should be performed. This is the target site.</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
-  </si>
-  <si>
-    <t>Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
-  </si>
-  <si>
-    <t>targetSiteCode</t>
-  </si>
-  <si>
-    <t>Procedure.targetBodySite</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>Justification de la demande d'examen / Finalité de l'examen</t>
-  </si>
-  <si>
-    <t>Any other notes and comments made about the service request. For example, internal billing notes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:text}
-</t>
-  </si>
-  <si>
-    <t>Request.note</t>
-  </si>
-  <si>
-    <t>.inboundRelationship(typeCode=SUBJ].source[classCode=ANNGEN, moodCode=EVN].value[xsi:type=ST]</t>
-  </si>
-  <si>
-    <t>ClinicalStatement.additionalText</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen</t>
-  </si>
-  <si>
-    <t>finaliteExamen</t>
-  </si>
-  <si>
-    <t>Finalité de l'examen demandé</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande</t>
-  </si>
-  <si>
-    <t>justificationDemande</t>
-  </si>
-  <si>
-    <t>Justification de la demande d'examen</t>
-  </si>
-  <si>
-    <t>ServiceRequest.patientInstruction</t>
   </si>
   <si>
     <t>Patient or consumer-oriented instructions</t>
@@ -1823,11 +1741,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO51"/>
+  <dimension ref="A1:AO47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.24609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="30.69921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.62109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1854,7 +1772,7 @@
     <col min="26" max="26" width="62.65234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.62109375" customWidth="true" bestFit="true" hidden="true"/>
@@ -4698,7 +4616,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4824,7 +4742,7 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>282</v>
@@ -4836,7 +4754,9 @@
         <v>284</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -4884,7 +4804,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4896,13 +4816,13 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>286</v>
@@ -4923,14 +4843,14 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -4939,20 +4859,18 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>288</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4989,65 +4907,65 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5059,20 +4977,16 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5120,13 +5034,13 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5135,35 +5049,35 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
@@ -5178,20 +5092,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5254,27 +5164,27 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5297,18 +5207,16 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>313</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5332,13 +5240,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5356,7 +5264,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5374,32 +5282,32 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>91</v>
@@ -5414,13 +5322,13 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5471,10 +5379,10 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>91</v>
@@ -5486,31 +5394,31 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5529,15 +5437,17 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5586,7 +5496,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5601,35 +5511,35 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>333</v>
+        <v>344</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>91</v>
@@ -5644,15 +5554,17 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>336</v>
+        <v>231</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5677,13 +5589,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5701,7 +5613,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5716,38 +5628,38 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5759,15 +5671,17 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5792,13 +5706,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -5816,13 +5730,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -5831,38 +5745,38 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -5874,13 +5788,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>354</v>
+        <v>231</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5907,13 +5821,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -5931,13 +5845,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -5946,38 +5860,38 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -5989,17 +5903,15 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6048,13 +5960,13 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
@@ -6063,38 +5975,38 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6109,13 +6021,13 @@
         <v>231</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6144,10 +6056,10 @@
         <v>236</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6165,13 +6077,13 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
@@ -6180,16 +6092,16 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6197,14 +6109,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6282,7 +6194,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6306,7 +6218,7 @@
         <v>392</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6337,16 +6249,16 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>231</v>
+        <v>394</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6373,13 +6285,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6412,16 +6324,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6429,14 +6341,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6452,18 +6364,20 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6512,7 +6426,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6527,16 +6441,16 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6544,10 +6458,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6570,16 +6484,16 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>231</v>
+        <v>410</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6605,13 +6519,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6629,7 +6543,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6644,16 +6558,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6661,14 +6575,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6687,18 +6601,20 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>414</v>
+        <v>231</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -6722,13 +6638,11 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6746,7 +6660,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6761,27 +6675,27 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6789,7 +6703,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>427</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>81</v>
@@ -6804,13 +6718,13 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6849,19 +6763,17 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6876,38 +6788,40 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>426</v>
+        <v>280</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="D44" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -6919,17 +6833,15 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L44" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>433</v>
-      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -6978,7 +6890,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6993,38 +6905,40 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7033,20 +6947,18 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7095,7 +7007,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7110,38 +7022,38 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>442</v>
+        <v>280</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7153,20 +7065,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>231</v>
+        <v>442</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7190,11 +7098,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7212,13 +7122,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -7230,24 +7140,24 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>442</v>
+        <v>280</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7255,7 +7165,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>81</v>
@@ -7270,15 +7180,17 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7315,17 +7227,19 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AC47" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7340,484 +7254,18 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>280</v>
+        <v>134</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="D48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:46:12+00:00</t>
+    <t>2026-07-23T09:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -869,7 +869,7 @@
 </t>
   </si>
   <si>
-    <t>Résultat de la demande</t>
+    <t>informations complémentaires sur la demande d'acte, exemple : INR cible</t>
   </si>
   <si>
     <t>Additional details and instructions about the how the services are to be delivered.   For example, and order for a urinary catheter may have an order detail for an external or indwelling catheter, or an order for a bandage may require additional instructions specifying how the bandage should be applied.</t>
@@ -2857,7 +2857,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>82</v>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="445">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:54:31+00:00</t>
+    <t>2026-07-23T10:00:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1350,23 +1350,16 @@
     <t>ServiceRequest.note</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Annotation
 </t>
   </si>
   <si>
-    <t>Justification de la demande d'examen / Finalité de l'examen</t>
+    <t>Note à propos de la demande d'acte, par exemple finalité de l'examen et justification de la demande</t>
   </si>
   <si>
     <t>Any other notes and comments made about the service request. For example, internal billing notes.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:text}
-</t>
-  </si>
-  <si>
     <t>Request.note</t>
   </si>
   <si>
@@ -1374,24 +1367,6 @@
   </si>
   <si>
     <t>ClinicalStatement.additionalText</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen</t>
-  </si>
-  <si>
-    <t>finaliteExamen</t>
-  </si>
-  <si>
-    <t>Finalité de l'examen demandé</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande</t>
-  </si>
-  <si>
-    <t>justificationDemande</t>
-  </si>
-  <si>
-    <t>Justification de la demande d'examen</t>
   </si>
   <si>
     <t>ServiceRequest.patientInstruction</t>
@@ -1741,12 +1716,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO47"/>
+  <dimension ref="A1:AO45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.24609375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.62109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.8984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -6703,7 +6678,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>81</v>
@@ -6718,13 +6693,13 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6763,14 +6738,16 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>426</v>
@@ -6788,37 +6765,35 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>280</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
@@ -6830,16 +6805,16 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6890,13 +6865,13 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
@@ -6905,19 +6880,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>280</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
@@ -6925,20 +6900,18 @@
         <v>438</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -6950,15 +6923,17 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>440</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7007,7 +6982,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7022,250 +6997,18 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>280</v>
+        <v>134</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O47" s="2"/>
-      <c r="P47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T10:00:41+00:00</t>
+    <t>2026-07-31T09:43:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:43:50+00:00</t>
+    <t>2026-07-31T14:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
